--- a/vse-loti/341412232/spec-341412232.xlsx
+++ b/vse-loti/341412232/spec-341412232.xlsx
@@ -84,7 +84,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -97,6 +97,9 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
@@ -465,7 +468,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I124"/>
+  <dimension ref="A1:I125"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -4619,8 +4622,15 @@
         <v>87691598.26000001</v>
       </c>
     </row>
-    <row r="122">
-      <c r="A122" s="10" t="inlineStr">
+    <row r="121">
+      <c r="A121" s="10" t="inlineStr">
+        <is>
+          <t>НДС 22 %, ставка определена по документу-источнику; суммы источника указаны без НДС: "Цена за единицу (предложение участника) без НДС" — 226219_190.26.00537_КОММ(АО Томская ген.).txt. «без НДС» — сумма из документа, «с НДС» = сумма × 1,22.</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="11" t="inlineStr">
         <is>
           <t>Источник: 226219_190.26.00537_КОММ(АО Томская ген.).xlsx
 226219_192.26.00972_КОММ(ТГК-11).xlsx
@@ -4630,11 +4640,11 @@
         </is>
       </c>
     </row>
-    <row r="123"/>
     <row r="124"/>
+    <row r="125"/>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A122:B124"/>
+    <mergeCell ref="A123:B125"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/vse-loti/341412232/spec-341412232.xlsx
+++ b/vse-loti/341412232/spec-341412232.xlsx
@@ -468,7 +468,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I125"/>
+  <dimension ref="A1:J125"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -480,6 +480,7 @@
     <col width="20.28515625" customWidth="1" min="7" max="7"/>
     <col width="18.85546875" customWidth="1" min="8" max="8"/>
     <col width="16.42578125" customWidth="1" min="9" max="9"/>
+    <col width="18.85546875" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
@@ -515,17 +516,22 @@
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
+          <t>Цена за т (без НДС)</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
           <t>Стоимость (без НДС)</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>Цена за т (без НДС)</t>
-        </is>
-      </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Цена за т (с НДС)</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Стоимость (с НДС)</t>
         </is>
       </c>
     </row>
@@ -555,13 +561,16 @@
         <v>1.15</v>
       </c>
       <c r="G2" s="5" t="n">
+        <v>115000</v>
+      </c>
+      <c r="H2" s="5" t="n">
         <v>132250</v>
-      </c>
-      <c r="H2" s="5" t="n">
-        <v>115000</v>
       </c>
       <c r="I2" s="5" t="n">
         <v>140300</v>
+      </c>
+      <c r="J2" s="5" t="n">
+        <v>161345</v>
       </c>
     </row>
     <row r="3">
@@ -590,13 +599,16 @@
         <v>1.64</v>
       </c>
       <c r="G3" s="5" t="n">
+        <v>115000</v>
+      </c>
+      <c r="H3" s="5" t="n">
         <v>188600</v>
-      </c>
-      <c r="H3" s="5" t="n">
-        <v>115000</v>
       </c>
       <c r="I3" s="5" t="n">
         <v>140300</v>
+      </c>
+      <c r="J3" s="5" t="n">
+        <v>230092</v>
       </c>
     </row>
     <row r="4">
@@ -625,13 +637,16 @@
         <v>0.01</v>
       </c>
       <c r="G4" s="5" t="n">
+        <v>115000</v>
+      </c>
+      <c r="H4" s="5" t="n">
         <v>1150</v>
-      </c>
-      <c r="H4" s="5" t="n">
-        <v>115000</v>
       </c>
       <c r="I4" s="5" t="n">
         <v>140300</v>
+      </c>
+      <c r="J4" s="5" t="n">
+        <v>1403</v>
       </c>
     </row>
     <row r="5">
@@ -660,13 +675,16 @@
         <v>0.273</v>
       </c>
       <c r="G5" s="5" t="n">
+        <v>115000</v>
+      </c>
+      <c r="H5" s="5" t="n">
         <v>31395</v>
-      </c>
-      <c r="H5" s="5" t="n">
-        <v>115000</v>
       </c>
       <c r="I5" s="5" t="n">
         <v>140300</v>
+      </c>
+      <c r="J5" s="5" t="n">
+        <v>38301.9</v>
       </c>
     </row>
     <row r="6">
@@ -695,13 +713,16 @@
         <v>0.5</v>
       </c>
       <c r="G6" s="5" t="n">
+        <v>115000</v>
+      </c>
+      <c r="H6" s="5" t="n">
         <v>57500</v>
-      </c>
-      <c r="H6" s="5" t="n">
-        <v>115000</v>
       </c>
       <c r="I6" s="5" t="n">
         <v>140300</v>
+      </c>
+      <c r="J6" s="5" t="n">
+        <v>70150</v>
       </c>
     </row>
     <row r="7">
@@ -730,13 +751,16 @@
         <v>1.02</v>
       </c>
       <c r="G7" s="5" t="n">
+        <v>115000</v>
+      </c>
+      <c r="H7" s="5" t="n">
         <v>117300</v>
-      </c>
-      <c r="H7" s="5" t="n">
-        <v>115000</v>
       </c>
       <c r="I7" s="5" t="n">
         <v>140300</v>
+      </c>
+      <c r="J7" s="5" t="n">
+        <v>143106</v>
       </c>
     </row>
     <row r="8">
@@ -765,13 +789,16 @@
         <v>0.05</v>
       </c>
       <c r="G8" s="5" t="n">
+        <v>114000</v>
+      </c>
+      <c r="H8" s="5" t="n">
         <v>5700</v>
-      </c>
-      <c r="H8" s="5" t="n">
-        <v>114000</v>
       </c>
       <c r="I8" s="5" t="n">
         <v>139080</v>
+      </c>
+      <c r="J8" s="5" t="n">
+        <v>6954</v>
       </c>
     </row>
     <row r="9">
@@ -800,13 +827,16 @@
         <v>0.6402</v>
       </c>
       <c r="G9" s="5" t="n">
+        <v>114000</v>
+      </c>
+      <c r="H9" s="5" t="n">
         <v>72988.5</v>
-      </c>
-      <c r="H9" s="5" t="n">
-        <v>114000</v>
       </c>
       <c r="I9" s="5" t="n">
         <v>139080</v>
+      </c>
+      <c r="J9" s="5" t="n">
+        <v>89045.97</v>
       </c>
     </row>
     <row r="10">
@@ -835,13 +865,16 @@
         <v>0.05</v>
       </c>
       <c r="G10" s="5" t="n">
+        <v>118000</v>
+      </c>
+      <c r="H10" s="5" t="n">
         <v>5900</v>
-      </c>
-      <c r="H10" s="5" t="n">
-        <v>118000</v>
       </c>
       <c r="I10" s="5" t="n">
         <v>143960</v>
+      </c>
+      <c r="J10" s="5" t="n">
+        <v>7198</v>
       </c>
     </row>
     <row r="11">
@@ -870,13 +903,16 @@
         <v>2.118</v>
       </c>
       <c r="G11" s="5" t="n">
+        <v>114000</v>
+      </c>
+      <c r="H11" s="5" t="n">
         <v>241456.56</v>
-      </c>
-      <c r="H11" s="5" t="n">
-        <v>114000</v>
       </c>
       <c r="I11" s="5" t="n">
         <v>139080</v>
+      </c>
+      <c r="J11" s="5" t="n">
+        <v>294577</v>
       </c>
     </row>
     <row r="12">
@@ -905,13 +941,16 @@
         <v>0.05</v>
       </c>
       <c r="G12" s="5" t="n">
+        <v>114000</v>
+      </c>
+      <c r="H12" s="5" t="n">
         <v>5700</v>
-      </c>
-      <c r="H12" s="5" t="n">
-        <v>114000</v>
       </c>
       <c r="I12" s="5" t="n">
         <v>139080</v>
+      </c>
+      <c r="J12" s="5" t="n">
+        <v>6954</v>
       </c>
     </row>
     <row r="13">
@@ -940,13 +979,16 @@
         <v>0.72</v>
       </c>
       <c r="G13" s="5" t="n">
+        <v>118000</v>
+      </c>
+      <c r="H13" s="5" t="n">
         <v>84960</v>
-      </c>
-      <c r="H13" s="5" t="n">
-        <v>118000</v>
       </c>
       <c r="I13" s="5" t="n">
         <v>143960</v>
+      </c>
+      <c r="J13" s="5" t="n">
+        <v>103651.2</v>
       </c>
     </row>
     <row r="14">
@@ -975,13 +1017,16 @@
         <v>0.08</v>
       </c>
       <c r="G14" s="5" t="n">
+        <v>115000</v>
+      </c>
+      <c r="H14" s="5" t="n">
         <v>9200</v>
-      </c>
-      <c r="H14" s="5" t="n">
-        <v>115000</v>
       </c>
       <c r="I14" s="5" t="n">
         <v>140300</v>
+      </c>
+      <c r="J14" s="5" t="n">
+        <v>11224</v>
       </c>
     </row>
     <row r="15">
@@ -1010,13 +1055,16 @@
         <v>1.247</v>
       </c>
       <c r="G15" s="5" t="n">
+        <v>115000</v>
+      </c>
+      <c r="H15" s="5" t="n">
         <v>143405</v>
-      </c>
-      <c r="H15" s="5" t="n">
-        <v>115000</v>
       </c>
       <c r="I15" s="5" t="n">
         <v>140300</v>
+      </c>
+      <c r="J15" s="5" t="n">
+        <v>174954.1</v>
       </c>
     </row>
     <row r="16">
@@ -1045,13 +1093,16 @@
         <v>0.167</v>
       </c>
       <c r="G16" s="5" t="n">
+        <v>115000</v>
+      </c>
+      <c r="H16" s="5" t="n">
         <v>19205</v>
-      </c>
-      <c r="H16" s="5" t="n">
-        <v>115000</v>
       </c>
       <c r="I16" s="5" t="n">
         <v>140300</v>
+      </c>
+      <c r="J16" s="5" t="n">
+        <v>23430.1</v>
       </c>
     </row>
     <row r="17">
@@ -1080,13 +1131,16 @@
         <v>0.007</v>
       </c>
       <c r="G17" s="5" t="n">
+        <v>115000</v>
+      </c>
+      <c r="H17" s="5" t="n">
         <v>805</v>
-      </c>
-      <c r="H17" s="5" t="n">
-        <v>115000</v>
       </c>
       <c r="I17" s="5" t="n">
         <v>140300</v>
+      </c>
+      <c r="J17" s="5" t="n">
+        <v>982.1</v>
       </c>
     </row>
     <row r="18">
@@ -1115,13 +1169,16 @@
         <v>0.01</v>
       </c>
       <c r="G18" s="5" t="n">
+        <v>115000</v>
+      </c>
+      <c r="H18" s="5" t="n">
         <v>1150</v>
-      </c>
-      <c r="H18" s="5" t="n">
-        <v>115000</v>
       </c>
       <c r="I18" s="5" t="n">
         <v>140300</v>
+      </c>
+      <c r="J18" s="5" t="n">
+        <v>1403</v>
       </c>
     </row>
     <row r="19">
@@ -1150,13 +1207,16 @@
         <v>0.01</v>
       </c>
       <c r="G19" s="5" t="n">
+        <v>115000</v>
+      </c>
+      <c r="H19" s="5" t="n">
         <v>1150</v>
-      </c>
-      <c r="H19" s="5" t="n">
-        <v>115000</v>
       </c>
       <c r="I19" s="5" t="n">
         <v>140300</v>
+      </c>
+      <c r="J19" s="5" t="n">
+        <v>1403</v>
       </c>
     </row>
     <row r="20">
@@ -1185,13 +1245,16 @@
         <v>2.24</v>
       </c>
       <c r="G20" s="5" t="n">
+        <v>90000</v>
+      </c>
+      <c r="H20" s="5" t="n">
         <v>201600</v>
-      </c>
-      <c r="H20" s="5" t="n">
-        <v>90000</v>
       </c>
       <c r="I20" s="5" t="n">
         <v>109800</v>
+      </c>
+      <c r="J20" s="5" t="n">
+        <v>245952</v>
       </c>
     </row>
     <row r="21">
@@ -1220,13 +1283,16 @@
         <v>8.507</v>
       </c>
       <c r="G21" s="5" t="n">
+        <v>90000</v>
+      </c>
+      <c r="H21" s="5" t="n">
         <v>765630</v>
-      </c>
-      <c r="H21" s="5" t="n">
-        <v>90000</v>
       </c>
       <c r="I21" s="5" t="n">
         <v>109800</v>
+      </c>
+      <c r="J21" s="5" t="n">
+        <v>934068.6</v>
       </c>
     </row>
     <row r="22">
@@ -1255,13 +1321,16 @@
         <v>2.565</v>
       </c>
       <c r="G22" s="5" t="n">
+        <v>90000</v>
+      </c>
+      <c r="H22" s="5" t="n">
         <v>230850</v>
-      </c>
-      <c r="H22" s="5" t="n">
-        <v>90000</v>
       </c>
       <c r="I22" s="5" t="n">
         <v>109800</v>
+      </c>
+      <c r="J22" s="5" t="n">
+        <v>281637</v>
       </c>
     </row>
     <row r="23">
@@ -1290,13 +1359,16 @@
         <v>0.11</v>
       </c>
       <c r="G23" s="5" t="n">
+        <v>90000</v>
+      </c>
+      <c r="H23" s="5" t="n">
         <v>9900</v>
-      </c>
-      <c r="H23" s="5" t="n">
-        <v>90000</v>
       </c>
       <c r="I23" s="5" t="n">
         <v>109800</v>
+      </c>
+      <c r="J23" s="5" t="n">
+        <v>12078</v>
       </c>
     </row>
     <row r="24">
@@ -1325,13 +1397,16 @@
         <v>0.713</v>
       </c>
       <c r="G24" s="5" t="n">
+        <v>90000</v>
+      </c>
+      <c r="H24" s="5" t="n">
         <v>64170</v>
-      </c>
-      <c r="H24" s="5" t="n">
-        <v>90000</v>
       </c>
       <c r="I24" s="5" t="n">
         <v>109800</v>
+      </c>
+      <c r="J24" s="5" t="n">
+        <v>78287.39999999999</v>
       </c>
     </row>
     <row r="25">
@@ -1360,13 +1435,16 @@
         <v>0.036</v>
       </c>
       <c r="G25" s="5" t="n">
+        <v>90000</v>
+      </c>
+      <c r="H25" s="5" t="n">
         <v>3240</v>
-      </c>
-      <c r="H25" s="5" t="n">
-        <v>90000</v>
       </c>
       <c r="I25" s="5" t="n">
         <v>109800</v>
+      </c>
+      <c r="J25" s="5" t="n">
+        <v>3952.8</v>
       </c>
     </row>
     <row r="26">
@@ -1395,13 +1473,16 @@
         <v>0.857</v>
       </c>
       <c r="G26" s="5" t="n">
+        <v>90000</v>
+      </c>
+      <c r="H26" s="5" t="n">
         <v>77130</v>
-      </c>
-      <c r="H26" s="5" t="n">
-        <v>90000</v>
       </c>
       <c r="I26" s="5" t="n">
         <v>109800</v>
+      </c>
+      <c r="J26" s="5" t="n">
+        <v>94098.60000000001</v>
       </c>
     </row>
     <row r="27">
@@ -1430,13 +1511,16 @@
         <v>0.3</v>
       </c>
       <c r="G27" s="5" t="n">
+        <v>90000</v>
+      </c>
+      <c r="H27" s="5" t="n">
         <v>27000</v>
-      </c>
-      <c r="H27" s="5" t="n">
-        <v>90000</v>
       </c>
       <c r="I27" s="5" t="n">
         <v>109800</v>
+      </c>
+      <c r="J27" s="5" t="n">
+        <v>32940</v>
       </c>
     </row>
     <row r="28">
@@ -1465,13 +1549,16 @@
         <v>0.996</v>
       </c>
       <c r="G28" s="5" t="n">
+        <v>90000</v>
+      </c>
+      <c r="H28" s="5" t="n">
         <v>89640</v>
-      </c>
-      <c r="H28" s="5" t="n">
-        <v>90000</v>
       </c>
       <c r="I28" s="5" t="n">
         <v>109800</v>
+      </c>
+      <c r="J28" s="5" t="n">
+        <v>109360.8</v>
       </c>
     </row>
     <row r="29">
@@ -1500,13 +1587,16 @@
         <v>0.93</v>
       </c>
       <c r="G29" s="5" t="n">
+        <v>70000</v>
+      </c>
+      <c r="H29" s="5" t="n">
         <v>65100</v>
-      </c>
-      <c r="H29" s="5" t="n">
-        <v>70000</v>
       </c>
       <c r="I29" s="5" t="n">
         <v>85400</v>
+      </c>
+      <c r="J29" s="5" t="n">
+        <v>79422</v>
       </c>
     </row>
     <row r="30">
@@ -1535,13 +1625,16 @@
         <v>4.285</v>
       </c>
       <c r="G30" s="5" t="n">
+        <v>90000</v>
+      </c>
+      <c r="H30" s="5" t="n">
         <v>385650</v>
-      </c>
-      <c r="H30" s="5" t="n">
-        <v>90000</v>
       </c>
       <c r="I30" s="5" t="n">
         <v>109800</v>
+      </c>
+      <c r="J30" s="5" t="n">
+        <v>470493</v>
       </c>
     </row>
     <row r="31">
@@ -1570,13 +1663,16 @@
         <v>3.4299</v>
       </c>
       <c r="G31" s="5" t="n">
+        <v>90000</v>
+      </c>
+      <c r="H31" s="5" t="n">
         <v>308691</v>
-      </c>
-      <c r="H31" s="5" t="n">
-        <v>90000</v>
       </c>
       <c r="I31" s="5" t="n">
         <v>109800</v>
+      </c>
+      <c r="J31" s="5" t="n">
+        <v>376603.02</v>
       </c>
     </row>
     <row r="32">
@@ -1605,13 +1701,16 @@
         <v>21.241</v>
       </c>
       <c r="G32" s="5" t="n">
+        <v>95000</v>
+      </c>
+      <c r="H32" s="5" t="n">
         <v>2017895</v>
-      </c>
-      <c r="H32" s="5" t="n">
-        <v>95000</v>
       </c>
       <c r="I32" s="5" t="n">
         <v>115900</v>
+      </c>
+      <c r="J32" s="5" t="n">
+        <v>2461831.9</v>
       </c>
     </row>
     <row r="33">
@@ -1640,13 +1739,16 @@
         <v>0.13</v>
       </c>
       <c r="G33" s="5" t="n">
+        <v>70000</v>
+      </c>
+      <c r="H33" s="5" t="n">
         <v>9100</v>
-      </c>
-      <c r="H33" s="5" t="n">
-        <v>70000</v>
       </c>
       <c r="I33" s="5" t="n">
         <v>85400</v>
+      </c>
+      <c r="J33" s="5" t="n">
+        <v>11102</v>
       </c>
     </row>
     <row r="34">
@@ -1675,13 +1777,16 @@
         <v>0.2</v>
       </c>
       <c r="G34" s="5" t="n">
+        <v>70000</v>
+      </c>
+      <c r="H34" s="5" t="n">
         <v>14000</v>
-      </c>
-      <c r="H34" s="5" t="n">
-        <v>70000</v>
       </c>
       <c r="I34" s="5" t="n">
         <v>85400</v>
+      </c>
+      <c r="J34" s="5" t="n">
+        <v>17080</v>
       </c>
     </row>
     <row r="35">
@@ -1710,13 +1815,16 @@
         <v>0.2</v>
       </c>
       <c r="G35" s="5" t="n">
+        <v>70000</v>
+      </c>
+      <c r="H35" s="5" t="n">
         <v>14000</v>
-      </c>
-      <c r="H35" s="5" t="n">
-        <v>70000</v>
       </c>
       <c r="I35" s="5" t="n">
         <v>85400</v>
+      </c>
+      <c r="J35" s="5" t="n">
+        <v>17080</v>
       </c>
     </row>
     <row r="36">
@@ -1745,13 +1853,16 @@
         <v>0.1</v>
       </c>
       <c r="G36" s="5" t="n">
+        <v>150000</v>
+      </c>
+      <c r="H36" s="5" t="n">
         <v>15000</v>
-      </c>
-      <c r="H36" s="5" t="n">
-        <v>150000</v>
       </c>
       <c r="I36" s="5" t="n">
         <v>183000</v>
+      </c>
+      <c r="J36" s="5" t="n">
+        <v>18300</v>
       </c>
     </row>
     <row r="37">
@@ -1780,13 +1891,16 @@
         <v>115.555</v>
       </c>
       <c r="G37" s="5" t="n">
+        <v>95000</v>
+      </c>
+      <c r="H37" s="5" t="n">
         <v>10977725</v>
-      </c>
-      <c r="H37" s="5" t="n">
-        <v>95000</v>
       </c>
       <c r="I37" s="5" t="n">
         <v>115900</v>
+      </c>
+      <c r="J37" s="5" t="n">
+        <v>13392824.5</v>
       </c>
     </row>
     <row r="38">
@@ -1815,13 +1929,16 @@
         <v>7</v>
       </c>
       <c r="G38" s="5" t="n">
+        <v>95000</v>
+      </c>
+      <c r="H38" s="5" t="n">
         <v>665000</v>
-      </c>
-      <c r="H38" s="5" t="n">
-        <v>95000</v>
       </c>
       <c r="I38" s="5" t="n">
         <v>115900</v>
+      </c>
+      <c r="J38" s="5" t="n">
+        <v>811300</v>
       </c>
     </row>
     <row r="39">
@@ -1850,13 +1967,16 @@
         <v>0.21</v>
       </c>
       <c r="G39" s="5" t="n">
+        <v>150000</v>
+      </c>
+      <c r="H39" s="5" t="n">
         <v>31500</v>
-      </c>
-      <c r="H39" s="5" t="n">
-        <v>150000</v>
       </c>
       <c r="I39" s="5" t="n">
         <v>183000</v>
+      </c>
+      <c r="J39" s="5" t="n">
+        <v>38430</v>
       </c>
     </row>
     <row r="40">
@@ -1885,13 +2005,16 @@
         <v>0.021</v>
       </c>
       <c r="G40" s="5" t="n">
+        <v>70000</v>
+      </c>
+      <c r="H40" s="5" t="n">
         <v>1470</v>
-      </c>
-      <c r="H40" s="5" t="n">
-        <v>70000</v>
       </c>
       <c r="I40" s="5" t="n">
         <v>85400</v>
+      </c>
+      <c r="J40" s="5" t="n">
+        <v>1793.4</v>
       </c>
     </row>
     <row r="41">
@@ -1920,13 +2043,16 @@
         <v>0.012</v>
       </c>
       <c r="G41" s="5" t="n">
+        <v>70000</v>
+      </c>
+      <c r="H41" s="5" t="n">
         <v>840</v>
-      </c>
-      <c r="H41" s="5" t="n">
-        <v>70000</v>
       </c>
       <c r="I41" s="5" t="n">
         <v>85400</v>
+      </c>
+      <c r="J41" s="5" t="n">
+        <v>1024.8</v>
       </c>
     </row>
     <row r="42">
@@ -1955,13 +2081,16 @@
         <v>1.4</v>
       </c>
       <c r="G42" s="5" t="n">
+        <v>150000</v>
+      </c>
+      <c r="H42" s="5" t="n">
         <v>210000</v>
-      </c>
-      <c r="H42" s="5" t="n">
-        <v>150000</v>
       </c>
       <c r="I42" s="5" t="n">
         <v>183000</v>
+      </c>
+      <c r="J42" s="5" t="n">
+        <v>256200</v>
       </c>
     </row>
     <row r="43">
@@ -1990,13 +2119,16 @@
         <v>2.8768</v>
       </c>
       <c r="G43" s="5" t="n">
+        <v>85000</v>
+      </c>
+      <c r="H43" s="5" t="n">
         <v>244527.15</v>
-      </c>
-      <c r="H43" s="5" t="n">
-        <v>85000</v>
       </c>
       <c r="I43" s="5" t="n">
         <v>103700</v>
+      </c>
+      <c r="J43" s="5" t="n">
+        <v>298323.12</v>
       </c>
     </row>
     <row r="44">
@@ -2025,13 +2157,16 @@
         <v>0.8219</v>
       </c>
       <c r="G44" s="5" t="n">
+        <v>85000</v>
+      </c>
+      <c r="H44" s="5" t="n">
         <v>69864.89999999999</v>
-      </c>
-      <c r="H44" s="5" t="n">
-        <v>85000</v>
       </c>
       <c r="I44" s="5" t="n">
         <v>103700</v>
+      </c>
+      <c r="J44" s="5" t="n">
+        <v>85235.17999999999</v>
       </c>
     </row>
     <row r="45">
@@ -2060,13 +2195,16 @@
         <v>0.4707</v>
       </c>
       <c r="G45" s="5" t="n">
+        <v>85000</v>
+      </c>
+      <c r="H45" s="5" t="n">
         <v>40009.5</v>
-      </c>
-      <c r="H45" s="5" t="n">
-        <v>85000</v>
       </c>
       <c r="I45" s="5" t="n">
         <v>103700</v>
+      </c>
+      <c r="J45" s="5" t="n">
+        <v>48811.59</v>
       </c>
     </row>
     <row r="46">
@@ -2095,13 +2233,16 @@
         <v>8.515000000000001</v>
       </c>
       <c r="G46" s="5" t="n">
+        <v>85000</v>
+      </c>
+      <c r="H46" s="5" t="n">
         <v>723775.85</v>
-      </c>
-      <c r="H46" s="5" t="n">
-        <v>85000</v>
       </c>
       <c r="I46" s="5" t="n">
         <v>103700</v>
+      </c>
+      <c r="J46" s="5" t="n">
+        <v>883006.54</v>
       </c>
     </row>
     <row r="47">
@@ -2130,13 +2271,16 @@
         <v>2.4329</v>
       </c>
       <c r="G47" s="5" t="n">
+        <v>85000</v>
+      </c>
+      <c r="H47" s="5" t="n">
         <v>206793.1</v>
-      </c>
-      <c r="H47" s="5" t="n">
-        <v>85000</v>
       </c>
       <c r="I47" s="5" t="n">
         <v>103700</v>
+      </c>
+      <c r="J47" s="5" t="n">
+        <v>252287.58</v>
       </c>
     </row>
     <row r="48">
@@ -2165,13 +2309,16 @@
         <v>1.257</v>
       </c>
       <c r="G48" s="5" t="n">
+        <v>85000</v>
+      </c>
+      <c r="H48" s="5" t="n">
         <v>106845</v>
-      </c>
-      <c r="H48" s="5" t="n">
-        <v>85000</v>
       </c>
       <c r="I48" s="5" t="n">
         <v>103700</v>
+      </c>
+      <c r="J48" s="5" t="n">
+        <v>130350.9</v>
       </c>
     </row>
     <row r="49">
@@ -2200,13 +2347,16 @@
         <v>0.015</v>
       </c>
       <c r="G49" s="5" t="n">
+        <v>65560</v>
+      </c>
+      <c r="H49" s="5" t="n">
         <v>983.4</v>
-      </c>
-      <c r="H49" s="5" t="n">
-        <v>65560</v>
       </c>
       <c r="I49" s="5" t="n">
         <v>79983.2</v>
+      </c>
+      <c r="J49" s="5" t="n">
+        <v>1199.75</v>
       </c>
     </row>
     <row r="50">
@@ -2235,13 +2385,16 @@
         <v>0.233</v>
       </c>
       <c r="G50" s="5" t="n">
+        <v>65560</v>
+      </c>
+      <c r="H50" s="5" t="n">
         <v>15275.48</v>
-      </c>
-      <c r="H50" s="5" t="n">
-        <v>65560</v>
       </c>
       <c r="I50" s="5" t="n">
         <v>79983.2</v>
+      </c>
+      <c r="J50" s="5" t="n">
+        <v>18636.09</v>
       </c>
     </row>
     <row r="51">
@@ -2270,13 +2423,16 @@
         <v>0.251</v>
       </c>
       <c r="G51" s="5" t="n">
+        <v>65560</v>
+      </c>
+      <c r="H51" s="5" t="n">
         <v>16452.28</v>
-      </c>
-      <c r="H51" s="5" t="n">
-        <v>65560</v>
       </c>
       <c r="I51" s="5" t="n">
         <v>79983.2</v>
+      </c>
+      <c r="J51" s="5" t="n">
+        <v>20071.78</v>
       </c>
     </row>
     <row r="52">
@@ -2305,13 +2461,16 @@
         <v>0.3626</v>
       </c>
       <c r="G52" s="5" t="n">
+        <v>65560</v>
+      </c>
+      <c r="H52" s="5" t="n">
         <v>23774.68</v>
-      </c>
-      <c r="H52" s="5" t="n">
-        <v>65560</v>
       </c>
       <c r="I52" s="5" t="n">
         <v>79983.2</v>
+      </c>
+      <c r="J52" s="5" t="n">
+        <v>29005.11</v>
       </c>
     </row>
     <row r="53">
@@ -2340,13 +2499,16 @@
         <v>0.1221</v>
       </c>
       <c r="G53" s="5" t="n">
+        <v>65560</v>
+      </c>
+      <c r="H53" s="5" t="n">
         <v>8004.48</v>
-      </c>
-      <c r="H53" s="5" t="n">
-        <v>65560</v>
       </c>
       <c r="I53" s="5" t="n">
         <v>79983.2</v>
+      </c>
+      <c r="J53" s="5" t="n">
+        <v>9765.469999999999</v>
       </c>
     </row>
     <row r="54">
@@ -2375,13 +2537,16 @@
         <v>0.12</v>
       </c>
       <c r="G54" s="5" t="n">
+        <v>65560</v>
+      </c>
+      <c r="H54" s="5" t="n">
         <v>7867.2</v>
-      </c>
-      <c r="H54" s="5" t="n">
-        <v>65560</v>
       </c>
       <c r="I54" s="5" t="n">
         <v>79983.2</v>
+      </c>
+      <c r="J54" s="5" t="n">
+        <v>9597.98</v>
       </c>
     </row>
     <row r="55">
@@ -2410,13 +2575,16 @@
         <v>0.1263</v>
       </c>
       <c r="G55" s="5" t="n">
+        <v>65560</v>
+      </c>
+      <c r="H55" s="5" t="n">
         <v>8278.26</v>
-      </c>
-      <c r="H55" s="5" t="n">
-        <v>65560</v>
       </c>
       <c r="I55" s="5" t="n">
         <v>79983.2</v>
+      </c>
+      <c r="J55" s="5" t="n">
+        <v>10099.48</v>
       </c>
     </row>
     <row r="56">
@@ -2445,13 +2613,16 @@
         <v>0.1835</v>
       </c>
       <c r="G56" s="5" t="n">
+        <v>86530</v>
+      </c>
+      <c r="H56" s="5" t="n">
         <v>15876.52</v>
-      </c>
-      <c r="H56" s="5" t="n">
-        <v>86530</v>
       </c>
       <c r="I56" s="5" t="n">
         <v>105566.6</v>
+      </c>
+      <c r="J56" s="5" t="n">
+        <v>19369.35</v>
       </c>
     </row>
     <row r="57">
@@ -2480,13 +2651,16 @@
         <v>0.0258</v>
       </c>
       <c r="G57" s="5" t="n">
+        <v>102270</v>
+      </c>
+      <c r="H57" s="5" t="n">
         <v>2638.57</v>
-      </c>
-      <c r="H57" s="5" t="n">
-        <v>102270</v>
       </c>
       <c r="I57" s="5" t="n">
         <v>124769.4</v>
+      </c>
+      <c r="J57" s="5" t="n">
+        <v>3219.06</v>
       </c>
     </row>
     <row r="58">
@@ -2515,13 +2689,16 @@
         <v>0.078</v>
       </c>
       <c r="G58" s="5" t="n">
+        <v>107920</v>
+      </c>
+      <c r="H58" s="5" t="n">
         <v>8417.76</v>
-      </c>
-      <c r="H58" s="5" t="n">
-        <v>107920</v>
       </c>
       <c r="I58" s="5" t="n">
         <v>131662.4</v>
+      </c>
+      <c r="J58" s="5" t="n">
+        <v>10269.67</v>
       </c>
     </row>
     <row r="59">
@@ -2550,13 +2727,16 @@
         <v>0.09</v>
       </c>
       <c r="G59" s="5" t="n">
+        <v>65560</v>
+      </c>
+      <c r="H59" s="5" t="n">
         <v>5900.4</v>
-      </c>
-      <c r="H59" s="5" t="n">
-        <v>65560</v>
       </c>
       <c r="I59" s="5" t="n">
         <v>79983.2</v>
+      </c>
+      <c r="J59" s="5" t="n">
+        <v>7198.49</v>
       </c>
     </row>
     <row r="60">
@@ -2585,13 +2765,16 @@
         <v>0.0713</v>
       </c>
       <c r="G60" s="5" t="n">
+        <v>65560</v>
+      </c>
+      <c r="H60" s="5" t="n">
         <v>4671.81</v>
-      </c>
-      <c r="H60" s="5" t="n">
-        <v>65560</v>
       </c>
       <c r="I60" s="5" t="n">
         <v>79983.2</v>
+      </c>
+      <c r="J60" s="5" t="n">
+        <v>5699.61</v>
       </c>
     </row>
     <row r="61">
@@ -2620,13 +2803,16 @@
         <v>0.4</v>
       </c>
       <c r="G61" s="5" t="n">
+        <v>69510</v>
+      </c>
+      <c r="H61" s="5" t="n">
         <v>27804</v>
-      </c>
-      <c r="H61" s="5" t="n">
-        <v>69510</v>
       </c>
       <c r="I61" s="5" t="n">
         <v>84802.2</v>
+      </c>
+      <c r="J61" s="5" t="n">
+        <v>33920.88</v>
       </c>
     </row>
     <row r="62">
@@ -2655,13 +2841,16 @@
         <v>0.6111</v>
       </c>
       <c r="G62" s="5" t="n">
+        <v>69510</v>
+      </c>
+      <c r="H62" s="5" t="n">
         <v>42477.28</v>
-      </c>
-      <c r="H62" s="5" t="n">
-        <v>69510</v>
       </c>
       <c r="I62" s="5" t="n">
         <v>84802.2</v>
+      </c>
+      <c r="J62" s="5" t="n">
+        <v>51822.28</v>
       </c>
     </row>
     <row r="63">
@@ -2690,13 +2879,16 @@
         <v>3.8114</v>
       </c>
       <c r="G63" s="5" t="n">
+        <v>62740</v>
+      </c>
+      <c r="H63" s="5" t="n">
         <v>239130.37</v>
-      </c>
-      <c r="H63" s="5" t="n">
-        <v>62740</v>
       </c>
       <c r="I63" s="5" t="n">
         <v>76542.8</v>
+      </c>
+      <c r="J63" s="5" t="n">
+        <v>291739.05</v>
       </c>
     </row>
     <row r="64">
@@ -2725,13 +2917,16 @@
         <v>0.025</v>
       </c>
       <c r="G64" s="5" t="n">
+        <v>69260</v>
+      </c>
+      <c r="H64" s="5" t="n">
         <v>1732.89</v>
-      </c>
-      <c r="H64" s="5" t="n">
-        <v>69260</v>
       </c>
       <c r="I64" s="5" t="n">
         <v>84497.2</v>
+      </c>
+      <c r="J64" s="5" t="n">
+        <v>2114.13</v>
       </c>
     </row>
     <row r="65">
@@ -2760,13 +2955,16 @@
         <v>2.036</v>
       </c>
       <c r="G65" s="5" t="n">
+        <v>88360</v>
+      </c>
+      <c r="H65" s="5" t="n">
         <v>179900.96</v>
-      </c>
-      <c r="H65" s="5" t="n">
-        <v>88360</v>
       </c>
       <c r="I65" s="5" t="n">
         <v>107799.2</v>
+      </c>
+      <c r="J65" s="5" t="n">
+        <v>219479.17</v>
       </c>
     </row>
     <row r="66">
@@ -2795,13 +2993,16 @@
         <v>0.2368</v>
       </c>
       <c r="G66" s="5" t="n">
+        <v>65850</v>
+      </c>
+      <c r="H66" s="5" t="n">
         <v>15590.65</v>
-      </c>
-      <c r="H66" s="5" t="n">
-        <v>65850</v>
       </c>
       <c r="I66" s="5" t="n">
         <v>80337</v>
+      </c>
+      <c r="J66" s="5" t="n">
+        <v>19020.59</v>
       </c>
     </row>
     <row r="67">
@@ -2830,13 +3031,16 @@
         <v>0.0436</v>
       </c>
       <c r="G67" s="5" t="n">
+        <v>65850</v>
+      </c>
+      <c r="H67" s="5" t="n">
         <v>2868.43</v>
-      </c>
-      <c r="H67" s="5" t="n">
-        <v>65850</v>
       </c>
       <c r="I67" s="5" t="n">
         <v>80337</v>
+      </c>
+      <c r="J67" s="5" t="n">
+        <v>3499.48</v>
       </c>
     </row>
     <row r="68">
@@ -2865,13 +3069,16 @@
         <v>0.092</v>
       </c>
       <c r="G68" s="5" t="n">
+        <v>146410</v>
+      </c>
+      <c r="H68" s="5" t="n">
         <v>13469.72</v>
-      </c>
-      <c r="H68" s="5" t="n">
-        <v>146410</v>
       </c>
       <c r="I68" s="5" t="n">
         <v>178620.2</v>
+      </c>
+      <c r="J68" s="5" t="n">
+        <v>16433.06</v>
       </c>
     </row>
     <row r="69">
@@ -2900,13 +3107,16 @@
         <v>0.0403</v>
       </c>
       <c r="G69" s="5" t="n">
+        <v>141780</v>
+      </c>
+      <c r="H69" s="5" t="n">
         <v>5716.57</v>
-      </c>
-      <c r="H69" s="5" t="n">
-        <v>141780</v>
       </c>
       <c r="I69" s="5" t="n">
         <v>172971.6</v>
+      </c>
+      <c r="J69" s="5" t="n">
+        <v>6974.22</v>
       </c>
     </row>
     <row r="70">
@@ -2935,13 +3145,16 @@
         <v>0.99</v>
       </c>
       <c r="G70" s="5" t="n">
+        <v>82500</v>
+      </c>
+      <c r="H70" s="5" t="n">
         <v>81675</v>
-      </c>
-      <c r="H70" s="5" t="n">
-        <v>82500</v>
       </c>
       <c r="I70" s="5" t="n">
         <v>100650</v>
+      </c>
+      <c r="J70" s="5" t="n">
+        <v>99643.5</v>
       </c>
     </row>
     <row r="71">
@@ -2970,13 +3183,16 @@
         <v>1.695</v>
       </c>
       <c r="G71" s="5" t="n">
+        <v>65560</v>
+      </c>
+      <c r="H71" s="5" t="n">
         <v>111124.2</v>
-      </c>
-      <c r="H71" s="5" t="n">
-        <v>65560</v>
       </c>
       <c r="I71" s="5" t="n">
         <v>79983.2</v>
+      </c>
+      <c r="J71" s="5" t="n">
+        <v>135571.52</v>
       </c>
     </row>
     <row r="72">
@@ -3005,13 +3221,16 @@
         <v>0.4029</v>
       </c>
       <c r="G72" s="5" t="n">
+        <v>65560</v>
+      </c>
+      <c r="H72" s="5" t="n">
         <v>26411.5</v>
-      </c>
-      <c r="H72" s="5" t="n">
-        <v>65560</v>
       </c>
       <c r="I72" s="5" t="n">
         <v>79983.2</v>
+      </c>
+      <c r="J72" s="5" t="n">
+        <v>32222.03</v>
       </c>
     </row>
     <row r="73">
@@ -3040,13 +3259,16 @@
         <v>79.752</v>
       </c>
       <c r="G73" s="5" t="n">
+        <v>76640</v>
+      </c>
+      <c r="H73" s="5" t="n">
         <v>6112193.28</v>
-      </c>
-      <c r="H73" s="5" t="n">
-        <v>76640</v>
       </c>
       <c r="I73" s="5" t="n">
         <v>93500.8</v>
+      </c>
+      <c r="J73" s="5" t="n">
+        <v>7456875.8</v>
       </c>
     </row>
     <row r="74">
@@ -3075,13 +3297,16 @@
         <v>9.723000000000001</v>
       </c>
       <c r="G74" s="5" t="n">
+        <v>76640</v>
+      </c>
+      <c r="H74" s="5" t="n">
         <v>745170.72</v>
-      </c>
-      <c r="H74" s="5" t="n">
-        <v>76640</v>
       </c>
       <c r="I74" s="5" t="n">
         <v>93500.8</v>
+      </c>
+      <c r="J74" s="5" t="n">
+        <v>909108.28</v>
       </c>
     </row>
     <row r="75">
@@ -3110,13 +3335,16 @@
         <v>12</v>
       </c>
       <c r="G75" s="5" t="n">
+        <v>76640</v>
+      </c>
+      <c r="H75" s="5" t="n">
         <v>919680</v>
-      </c>
-      <c r="H75" s="5" t="n">
-        <v>76640</v>
       </c>
       <c r="I75" s="5" t="n">
         <v>93500.8</v>
+      </c>
+      <c r="J75" s="5" t="n">
+        <v>1122009.6</v>
       </c>
     </row>
     <row r="76">
@@ -3145,13 +3373,16 @@
         <v>88.867</v>
       </c>
       <c r="G76" s="5" t="n">
+        <v>77310</v>
+      </c>
+      <c r="H76" s="5" t="n">
         <v>6870307.77</v>
-      </c>
-      <c r="H76" s="5" t="n">
-        <v>77310</v>
       </c>
       <c r="I76" s="5" t="n">
         <v>94318.2</v>
+      </c>
+      <c r="J76" s="5" t="n">
+        <v>8381775.48</v>
       </c>
     </row>
     <row r="77">
@@ -3180,13 +3411,16 @@
         <v>18.312</v>
       </c>
       <c r="G77" s="5" t="n">
+        <v>77310</v>
+      </c>
+      <c r="H77" s="5" t="n">
         <v>1415700.72</v>
-      </c>
-      <c r="H77" s="5" t="n">
-        <v>77310</v>
       </c>
       <c r="I77" s="5" t="n">
         <v>94318.2</v>
+      </c>
+      <c r="J77" s="5" t="n">
+        <v>1727154.88</v>
       </c>
     </row>
     <row r="78">
@@ -3215,13 +3449,16 @@
         <v>15</v>
       </c>
       <c r="G78" s="5" t="n">
+        <v>77310</v>
+      </c>
+      <c r="H78" s="5" t="n">
         <v>1159650</v>
-      </c>
-      <c r="H78" s="5" t="n">
-        <v>77310</v>
       </c>
       <c r="I78" s="5" t="n">
         <v>94318.2</v>
+      </c>
+      <c r="J78" s="5" t="n">
+        <v>1414773</v>
       </c>
     </row>
     <row r="79">
@@ -3250,13 +3487,16 @@
         <v>0.136</v>
       </c>
       <c r="G79" s="5" t="n">
+        <v>79630</v>
+      </c>
+      <c r="H79" s="5" t="n">
         <v>10829.68</v>
-      </c>
-      <c r="H79" s="5" t="n">
-        <v>79630</v>
       </c>
       <c r="I79" s="5" t="n">
         <v>97148.60000000001</v>
+      </c>
+      <c r="J79" s="5" t="n">
+        <v>13212.21</v>
       </c>
     </row>
     <row r="80">
@@ -3285,13 +3525,16 @@
         <v>0.268</v>
       </c>
       <c r="G80" s="5" t="n">
+        <v>80340</v>
+      </c>
+      <c r="H80" s="5" t="n">
         <v>21531.12</v>
-      </c>
-      <c r="H80" s="5" t="n">
-        <v>80340</v>
       </c>
       <c r="I80" s="5" t="n">
         <v>98014.8</v>
+      </c>
+      <c r="J80" s="5" t="n">
+        <v>26267.97</v>
       </c>
     </row>
     <row r="81">
@@ -3320,13 +3563,16 @@
         <v>0.219</v>
       </c>
       <c r="G81" s="5" t="n">
+        <v>78680</v>
+      </c>
+      <c r="H81" s="5" t="n">
         <v>17230.92</v>
-      </c>
-      <c r="H81" s="5" t="n">
-        <v>78680</v>
       </c>
       <c r="I81" s="5" t="n">
         <v>95989.60000000001</v>
+      </c>
+      <c r="J81" s="5" t="n">
+        <v>21021.72</v>
       </c>
     </row>
     <row r="82">
@@ -3355,13 +3601,16 @@
         <v>0.5838</v>
       </c>
       <c r="G82" s="5" t="n">
+        <v>79040</v>
+      </c>
+      <c r="H82" s="5" t="n">
         <v>46143.55</v>
-      </c>
-      <c r="H82" s="5" t="n">
-        <v>79040</v>
       </c>
       <c r="I82" s="5" t="n">
         <v>96428.8</v>
+      </c>
+      <c r="J82" s="5" t="n">
+        <v>56295.13</v>
       </c>
     </row>
     <row r="83">
@@ -3390,13 +3639,16 @@
         <v>0.642</v>
       </c>
       <c r="G83" s="5" t="n">
+        <v>78270</v>
+      </c>
+      <c r="H83" s="5" t="n">
         <v>50249.34</v>
-      </c>
-      <c r="H83" s="5" t="n">
-        <v>78270</v>
       </c>
       <c r="I83" s="5" t="n">
         <v>95489.39999999999</v>
+      </c>
+      <c r="J83" s="5" t="n">
+        <v>61304.19</v>
       </c>
     </row>
     <row r="84">
@@ -3425,13 +3677,16 @@
         <v>0.298</v>
       </c>
       <c r="G84" s="5" t="n">
+        <v>58720</v>
+      </c>
+      <c r="H84" s="5" t="n">
         <v>17498.56</v>
-      </c>
-      <c r="H84" s="5" t="n">
-        <v>58720</v>
       </c>
       <c r="I84" s="5" t="n">
         <v>71638.39999999999</v>
+      </c>
+      <c r="J84" s="5" t="n">
+        <v>21348.24</v>
       </c>
     </row>
     <row r="85">
@@ -3460,13 +3715,16 @@
         <v>1.888</v>
       </c>
       <c r="G85" s="5" t="n">
+        <v>76500</v>
+      </c>
+      <c r="H85" s="5" t="n">
         <v>144432</v>
-      </c>
-      <c r="H85" s="5" t="n">
-        <v>76500</v>
       </c>
       <c r="I85" s="5" t="n">
         <v>93330</v>
+      </c>
+      <c r="J85" s="5" t="n">
+        <v>176207.04</v>
       </c>
     </row>
     <row r="86">
@@ -3495,13 +3753,16 @@
         <v>32.971</v>
       </c>
       <c r="G86" s="5" t="n">
+        <v>76500</v>
+      </c>
+      <c r="H86" s="5" t="n">
         <v>2522281.5</v>
-      </c>
-      <c r="H86" s="5" t="n">
-        <v>76500</v>
       </c>
       <c r="I86" s="5" t="n">
         <v>93330</v>
+      </c>
+      <c r="J86" s="5" t="n">
+        <v>3077183.43</v>
       </c>
     </row>
     <row r="87">
@@ -3530,13 +3791,16 @@
         <v>5</v>
       </c>
       <c r="G87" s="5" t="n">
+        <v>76500</v>
+      </c>
+      <c r="H87" s="5" t="n">
         <v>382500</v>
-      </c>
-      <c r="H87" s="5" t="n">
-        <v>76500</v>
       </c>
       <c r="I87" s="5" t="n">
         <v>93330</v>
+      </c>
+      <c r="J87" s="5" t="n">
+        <v>466650</v>
       </c>
     </row>
     <row r="88">
@@ -3565,13 +3829,16 @@
         <v>3.52</v>
       </c>
       <c r="G88" s="5" t="n">
+        <v>77730</v>
+      </c>
+      <c r="H88" s="5" t="n">
         <v>273609.6</v>
-      </c>
-      <c r="H88" s="5" t="n">
-        <v>77730</v>
       </c>
       <c r="I88" s="5" t="n">
         <v>94830.60000000001</v>
+      </c>
+      <c r="J88" s="5" t="n">
+        <v>333803.71</v>
       </c>
     </row>
     <row r="89">
@@ -3600,13 +3867,16 @@
         <v>42.496</v>
       </c>
       <c r="G89" s="5" t="n">
+        <v>77730</v>
+      </c>
+      <c r="H89" s="5" t="n">
         <v>3303214.08</v>
-      </c>
-      <c r="H89" s="5" t="n">
-        <v>77730</v>
       </c>
       <c r="I89" s="5" t="n">
         <v>94830.60000000001</v>
+      </c>
+      <c r="J89" s="5" t="n">
+        <v>4029921.18</v>
       </c>
     </row>
     <row r="90">
@@ -3635,13 +3905,16 @@
         <v>5</v>
       </c>
       <c r="G90" s="5" t="n">
+        <v>77730</v>
+      </c>
+      <c r="H90" s="5" t="n">
         <v>388650</v>
-      </c>
-      <c r="H90" s="5" t="n">
-        <v>77730</v>
       </c>
       <c r="I90" s="5" t="n">
         <v>94830.60000000001</v>
+      </c>
+      <c r="J90" s="5" t="n">
+        <v>474153</v>
       </c>
     </row>
     <row r="91">
@@ -3670,13 +3943,16 @@
         <v>69.074</v>
       </c>
       <c r="G91" s="5" t="n">
+        <v>77060</v>
+      </c>
+      <c r="H91" s="5" t="n">
         <v>5322842.44</v>
-      </c>
-      <c r="H91" s="5" t="n">
-        <v>77060</v>
       </c>
       <c r="I91" s="5" t="n">
         <v>94013.2</v>
+      </c>
+      <c r="J91" s="5" t="n">
+        <v>6493867.78</v>
       </c>
     </row>
     <row r="92">
@@ -3705,13 +3981,16 @@
         <v>6.258</v>
       </c>
       <c r="G92" s="5" t="n">
+        <v>77060</v>
+      </c>
+      <c r="H92" s="5" t="n">
         <v>482241.48</v>
-      </c>
-      <c r="H92" s="5" t="n">
-        <v>77060</v>
       </c>
       <c r="I92" s="5" t="n">
         <v>94013.2</v>
+      </c>
+      <c r="J92" s="5" t="n">
+        <v>588334.61</v>
       </c>
     </row>
     <row r="93">
@@ -3740,13 +4019,16 @@
         <v>10</v>
       </c>
       <c r="G93" s="5" t="n">
+        <v>77060</v>
+      </c>
+      <c r="H93" s="5" t="n">
         <v>770600</v>
-      </c>
-      <c r="H93" s="5" t="n">
-        <v>77060</v>
       </c>
       <c r="I93" s="5" t="n">
         <v>94013.2</v>
+      </c>
+      <c r="J93" s="5" t="n">
+        <v>940132</v>
       </c>
     </row>
     <row r="94">
@@ -3775,13 +4057,16 @@
         <v>4.46</v>
       </c>
       <c r="G94" s="5" t="n">
+        <v>99250</v>
+      </c>
+      <c r="H94" s="5" t="n">
         <v>442655</v>
-      </c>
-      <c r="H94" s="5" t="n">
-        <v>99250</v>
       </c>
       <c r="I94" s="5" t="n">
         <v>121085</v>
+      </c>
+      <c r="J94" s="5" t="n">
+        <v>540039.1</v>
       </c>
     </row>
     <row r="95">
@@ -3810,13 +4095,16 @@
         <v>48.424</v>
       </c>
       <c r="G95" s="5" t="n">
+        <v>99250</v>
+      </c>
+      <c r="H95" s="5" t="n">
         <v>4806082</v>
-      </c>
-      <c r="H95" s="5" t="n">
-        <v>99250</v>
       </c>
       <c r="I95" s="5" t="n">
         <v>121085</v>
+      </c>
+      <c r="J95" s="5" t="n">
+        <v>5863420.04</v>
       </c>
     </row>
     <row r="96">
@@ -3845,13 +4133,16 @@
         <v>15</v>
       </c>
       <c r="G96" s="5" t="n">
+        <v>99250</v>
+      </c>
+      <c r="H96" s="5" t="n">
         <v>1488750</v>
-      </c>
-      <c r="H96" s="5" t="n">
-        <v>99250</v>
       </c>
       <c r="I96" s="5" t="n">
         <v>121085</v>
+      </c>
+      <c r="J96" s="5" t="n">
+        <v>1816275</v>
       </c>
     </row>
     <row r="97">
@@ -3880,13 +4171,16 @@
         <v>0.543</v>
       </c>
       <c r="G97" s="5" t="n">
+        <v>87090</v>
+      </c>
+      <c r="H97" s="5" t="n">
         <v>47289.87</v>
-      </c>
-      <c r="H97" s="5" t="n">
-        <v>87090</v>
       </c>
       <c r="I97" s="5" t="n">
         <v>106249.8</v>
+      </c>
+      <c r="J97" s="5" t="n">
+        <v>57693.64</v>
       </c>
     </row>
     <row r="98">
@@ -3915,13 +4209,16 @@
         <v>24.244</v>
       </c>
       <c r="G98" s="5" t="n">
+        <v>87090</v>
+      </c>
+      <c r="H98" s="5" t="n">
         <v>2111409.96</v>
-      </c>
-      <c r="H98" s="5" t="n">
-        <v>87090</v>
       </c>
       <c r="I98" s="5" t="n">
         <v>106249.8</v>
+      </c>
+      <c r="J98" s="5" t="n">
+        <v>2575920.15</v>
       </c>
     </row>
     <row r="99">
@@ -3950,13 +4247,16 @@
         <v>15</v>
       </c>
       <c r="G99" s="5" t="n">
+        <v>87090</v>
+      </c>
+      <c r="H99" s="5" t="n">
         <v>1306350</v>
-      </c>
-      <c r="H99" s="5" t="n">
-        <v>87090</v>
       </c>
       <c r="I99" s="5" t="n">
         <v>106249.8</v>
+      </c>
+      <c r="J99" s="5" t="n">
+        <v>1593747</v>
       </c>
     </row>
     <row r="100">
@@ -3985,13 +4285,16 @@
         <v>2.843</v>
       </c>
       <c r="G100" s="5" t="n">
+        <v>87410</v>
+      </c>
+      <c r="H100" s="5" t="n">
         <v>248506.63</v>
-      </c>
-      <c r="H100" s="5" t="n">
-        <v>87410</v>
       </c>
       <c r="I100" s="5" t="n">
         <v>106640.2</v>
+      </c>
+      <c r="J100" s="5" t="n">
+        <v>303178.09</v>
       </c>
     </row>
     <row r="101">
@@ -4020,13 +4323,16 @@
         <v>26.671</v>
       </c>
       <c r="G101" s="5" t="n">
+        <v>87410</v>
+      </c>
+      <c r="H101" s="5" t="n">
         <v>2331312.11</v>
-      </c>
-      <c r="H101" s="5" t="n">
-        <v>87410</v>
       </c>
       <c r="I101" s="5" t="n">
         <v>106640.2</v>
+      </c>
+      <c r="J101" s="5" t="n">
+        <v>2844200.77</v>
       </c>
     </row>
     <row r="102">
@@ -4055,13 +4361,16 @@
         <v>10</v>
       </c>
       <c r="G102" s="5" t="n">
+        <v>87410</v>
+      </c>
+      <c r="H102" s="5" t="n">
         <v>874100</v>
-      </c>
-      <c r="H102" s="5" t="n">
-        <v>87410</v>
       </c>
       <c r="I102" s="5" t="n">
         <v>106640.2</v>
+      </c>
+      <c r="J102" s="5" t="n">
+        <v>1066402</v>
       </c>
     </row>
     <row r="103">
@@ -4090,13 +4399,16 @@
         <v>5.167</v>
       </c>
       <c r="G103" s="5" t="n">
+        <v>92310</v>
+      </c>
+      <c r="H103" s="5" t="n">
         <v>476965.77</v>
-      </c>
-      <c r="H103" s="5" t="n">
-        <v>92310</v>
       </c>
       <c r="I103" s="5" t="n">
         <v>112618.2</v>
+      </c>
+      <c r="J103" s="5" t="n">
+        <v>581898.24</v>
       </c>
     </row>
     <row r="104">
@@ -4125,13 +4437,16 @@
         <v>5.194</v>
       </c>
       <c r="G104" s="5" t="n">
+        <v>92310</v>
+      </c>
+      <c r="H104" s="5" t="n">
         <v>479458.14</v>
-      </c>
-      <c r="H104" s="5" t="n">
-        <v>92310</v>
       </c>
       <c r="I104" s="5" t="n">
         <v>112618.2</v>
+      </c>
+      <c r="J104" s="5" t="n">
+        <v>584938.9300000001</v>
       </c>
     </row>
     <row r="105">
@@ -4160,13 +4475,16 @@
         <v>6</v>
       </c>
       <c r="G105" s="5" t="n">
+        <v>92310</v>
+      </c>
+      <c r="H105" s="5" t="n">
         <v>553860</v>
-      </c>
-      <c r="H105" s="5" t="n">
-        <v>92310</v>
       </c>
       <c r="I105" s="5" t="n">
         <v>112618.2</v>
+      </c>
+      <c r="J105" s="5" t="n">
+        <v>675709.2</v>
       </c>
     </row>
     <row r="106">
@@ -4195,13 +4513,16 @@
         <v>12.145</v>
       </c>
       <c r="G106" s="5" t="n">
+        <v>92310</v>
+      </c>
+      <c r="H106" s="5" t="n">
         <v>1121104.95</v>
-      </c>
-      <c r="H106" s="5" t="n">
-        <v>92310</v>
       </c>
       <c r="I106" s="5" t="n">
         <v>112618.2</v>
+      </c>
+      <c r="J106" s="5" t="n">
+        <v>1367748.04</v>
       </c>
     </row>
     <row r="107">
@@ -4230,13 +4551,16 @@
         <v>5.157</v>
       </c>
       <c r="G107" s="5" t="n">
+        <v>92310</v>
+      </c>
+      <c r="H107" s="5" t="n">
         <v>476042.67</v>
-      </c>
-      <c r="H107" s="5" t="n">
-        <v>92310</v>
       </c>
       <c r="I107" s="5" t="n">
         <v>112618.2</v>
+      </c>
+      <c r="J107" s="5" t="n">
+        <v>580772.0600000001</v>
       </c>
     </row>
     <row r="108">
@@ -4265,13 +4589,16 @@
         <v>15</v>
       </c>
       <c r="G108" s="5" t="n">
+        <v>92310</v>
+      </c>
+      <c r="H108" s="5" t="n">
         <v>1384650</v>
-      </c>
-      <c r="H108" s="5" t="n">
-        <v>92310</v>
       </c>
       <c r="I108" s="5" t="n">
         <v>112618.2</v>
+      </c>
+      <c r="J108" s="5" t="n">
+        <v>1689273</v>
       </c>
     </row>
     <row r="109">
@@ -4300,13 +4627,16 @@
         <v>13.341</v>
       </c>
       <c r="G109" s="5" t="n">
+        <v>80000</v>
+      </c>
+      <c r="H109" s="5" t="n">
         <v>1067280</v>
-      </c>
-      <c r="H109" s="5" t="n">
-        <v>80000</v>
       </c>
       <c r="I109" s="5" t="n">
         <v>97600</v>
+      </c>
+      <c r="J109" s="5" t="n">
+        <v>1302081.6</v>
       </c>
     </row>
     <row r="110">
@@ -4335,13 +4665,16 @@
         <v>0.02</v>
       </c>
       <c r="G110" s="5" t="n">
+        <v>70000</v>
+      </c>
+      <c r="H110" s="5" t="n">
         <v>1400</v>
-      </c>
-      <c r="H110" s="5" t="n">
-        <v>70000</v>
       </c>
       <c r="I110" s="5" t="n">
         <v>85400</v>
+      </c>
+      <c r="J110" s="5" t="n">
+        <v>1708</v>
       </c>
     </row>
     <row r="111">
@@ -4370,13 +4703,16 @@
         <v>0.07140000000000001</v>
       </c>
       <c r="G111" s="5" t="n">
+        <v>70000</v>
+      </c>
+      <c r="H111" s="5" t="n">
         <v>4998</v>
-      </c>
-      <c r="H111" s="5" t="n">
-        <v>70000</v>
       </c>
       <c r="I111" s="5" t="n">
         <v>85400</v>
+      </c>
+      <c r="J111" s="5" t="n">
+        <v>6097.56</v>
       </c>
     </row>
     <row r="112">
@@ -4405,13 +4741,16 @@
         <v>0.451</v>
       </c>
       <c r="G112" s="5" t="n">
+        <v>80000</v>
+      </c>
+      <c r="H112" s="5" t="n">
         <v>36080</v>
-      </c>
-      <c r="H112" s="5" t="n">
-        <v>80000</v>
       </c>
       <c r="I112" s="5" t="n">
         <v>97600</v>
+      </c>
+      <c r="J112" s="5" t="n">
+        <v>44017.6</v>
       </c>
     </row>
     <row r="113">
@@ -4440,13 +4779,16 @@
         <v>5.4452</v>
       </c>
       <c r="G113" s="5" t="n">
+        <v>70000</v>
+      </c>
+      <c r="H113" s="5" t="n">
         <v>381164</v>
-      </c>
-      <c r="H113" s="5" t="n">
-        <v>70000</v>
       </c>
       <c r="I113" s="5" t="n">
         <v>85400</v>
+      </c>
+      <c r="J113" s="5" t="n">
+        <v>465020.08</v>
       </c>
     </row>
     <row r="114">
@@ -4475,13 +4817,16 @@
         <v>7.254</v>
       </c>
       <c r="G114" s="5" t="n">
+        <v>85000</v>
+      </c>
+      <c r="H114" s="5" t="n">
         <v>616590</v>
-      </c>
-      <c r="H114" s="5" t="n">
-        <v>85000</v>
       </c>
       <c r="I114" s="5" t="n">
         <v>103700</v>
+      </c>
+      <c r="J114" s="5" t="n">
+        <v>752239.8</v>
       </c>
     </row>
     <row r="115">
@@ -4510,13 +4855,16 @@
         <v>0.712</v>
       </c>
       <c r="G115" s="5" t="n">
+        <v>70000</v>
+      </c>
+      <c r="H115" s="5" t="n">
         <v>49840</v>
-      </c>
-      <c r="H115" s="5" t="n">
-        <v>70000</v>
       </c>
       <c r="I115" s="5" t="n">
         <v>85400</v>
+      </c>
+      <c r="J115" s="5" t="n">
+        <v>60804.8</v>
       </c>
     </row>
     <row r="116">
@@ -4545,13 +4893,16 @@
         <v>1.231</v>
       </c>
       <c r="G116" s="5" t="n">
+        <v>80000</v>
+      </c>
+      <c r="H116" s="5" t="n">
         <v>98480</v>
-      </c>
-      <c r="H116" s="5" t="n">
-        <v>80000</v>
       </c>
       <c r="I116" s="5" t="n">
         <v>97600</v>
+      </c>
+      <c r="J116" s="5" t="n">
+        <v>120145.6</v>
       </c>
     </row>
     <row r="117">
@@ -4580,14 +4931,17 @@
         <v>10.9956</v>
       </c>
       <c r="G117" s="5" t="n">
+        <v>85000</v>
+      </c>
+      <c r="H117" s="5" t="n">
         <v>934629.4</v>
-      </c>
-      <c r="H117" s="5" t="n">
-        <v>85000</v>
       </c>
       <c r="I117" s="5" t="n">
         <v>103700</v>
       </c>
+      <c r="J117" s="5" t="n">
+        <v>1140247.87</v>
+      </c>
     </row>
     <row r="118">
       <c r="A118" s="7" t="inlineStr">
@@ -4599,7 +4953,16 @@
         <v>846.5941</v>
       </c>
       <c r="G118" s="9" t="n">
+        <v>84902.98</v>
+      </c>
+      <c r="H118" s="9" t="n">
         <v>71878359.23</v>
+      </c>
+      <c r="I118" s="9" t="n">
+        <v>103581.64</v>
+      </c>
+      <c r="J118" s="9" t="n">
+        <v>87691598.26000001</v>
       </c>
     </row>
     <row r="119">
@@ -4608,7 +4971,7 @@
           <t>НМЦК из обоснования:</t>
         </is>
       </c>
-      <c r="G119" s="9" t="n">
+      <c r="H119" s="9" t="n">
         <v>71878359.22660002</v>
       </c>
     </row>
@@ -4618,7 +4981,7 @@
           <t>НМЦК с НДС 22%:</t>
         </is>
       </c>
-      <c r="F120" s="9" t="n">
+      <c r="J120" s="9" t="n">
         <v>87691598.26000001</v>
       </c>
     </row>
